--- a/decks/eloqwnt/keyword-research-ai.xlsx
+++ b/decks/eloqwnt/keyword-research-ai.xlsx
@@ -43,11 +43,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00155724"/>
+      <color rgb="009C4221"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C4221"/>
+      <color rgb="00155724"/>
     </font>
     <font>
       <color rgb="006c757d"/>
@@ -86,22 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B942"/>
+        <fgColor rgb="007BC043"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF2D8E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007BC043"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +106,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4B942"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007B2FF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,13 +164,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,7 +179,7 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -625,23 +625,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Logo: What an AI-Native Studio Delivers</t>
+          <t>AI Design Subscription: What an AI-Native Studio Delivers</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>artificial intelligence logo</t>
+          <t>ai design subscription</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1600</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -669,23 +669,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Design Subscription: What an AI-Native Studio Delivers</t>
+          <t>AI Branding Agency: AI Speed, Human Craft</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ai design subscription</t>
+          <t>ai branding agency</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -693,7 +693,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -713,12 +713,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AI Branding Agency: AI Speed, Human Craft</t>
+          <t>AI Web Design Agency: What an AI-Native Studio Delivers</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ai branding agency</t>
+          <t>ai web design agency</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -727,7 +727,7 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -737,7 +737,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -757,12 +757,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI Web Design Agency: What an AI-Native Studio Delivers</t>
+          <t>Choosing an AI Design Agency: A 2026 Buyer's Guide</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>ai web design agency</t>
+          <t>ai design agency</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -771,7 +771,7 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -781,7 +781,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -801,21 +801,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Choosing AI Design Agency: A 2026 Buyer's Guide</t>
+          <t>AI UX Design Agency: Faster and Leaner, Still Human</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>ai design agency</t>
+          <t>ai ux design agency</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -825,7 +825,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -845,21 +845,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI UX Design Agency: Faster and Leaner, Still Human</t>
+          <t>AI Webflow Agency: What to Expect &amp; How It Works</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ai ux design agency</t>
+          <t>ai webflow agency</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -869,7 +869,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -889,21 +889,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AI Webflow Agency: What to Expect &amp; How It Works</t>
+          <t>Why Work With a Generative AI Design Agency</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ai webflow agency</t>
+          <t>generative ai design agency</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -913,7 +913,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -933,21 +933,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why Work With Generative AI Design Agency</t>
+          <t>AI Brand Strategy Agency: The AI-Plus-Human Advantage</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>generative ai design agency</t>
+          <t>ai brand strategy agency</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -957,7 +957,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -977,21 +977,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AI Brand Strategy Agency: The AI-Plus-Human Advantage</t>
+          <t>AI Product Design Agency: AI Speed, Human Craft</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ai brand strategy agency</t>
+          <t>ai product design agency</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1001,7 +1001,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1021,21 +1021,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AI Product Design Agency: AI Speed, Human Craft</t>
+          <t>Choosing an AI Branding Studio: A 2026 Buyer's Guide</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ai product design agency</t>
+          <t>ai branding studio</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1045,7 +1045,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1065,21 +1065,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Choosing AI Branding Studio: A 2026 Buyer's Guide</t>
+          <t>AI Web Design Studio: Faster and Leaner, Still Human</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ai branding studio</t>
+          <t>ai web design studio</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1089,7 +1089,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AI Web Design Studio: Faster and Leaner, Still Human</t>
+          <t>AI-Powered Branding Agency: What to Expect &amp; How It Works</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ai web design studio</t>
+          <t>ai powered branding agency</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -1123,7 +1123,7 @@
       <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1133,7 +1133,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1153,21 +1153,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI Powered Branding Agency: What to Expect &amp; How It Works</t>
+          <t>Why Work With an AI-First Design Agency</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ai powered branding agency</t>
+          <t>ai first design agency</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1177,7 +1177,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1197,21 +1197,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why Work With AI First Design Agency</t>
+          <t>AI UI/UX Agency: The AI-Plus-Human Advantage</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ai first design agency</t>
+          <t>ai ui ux agency</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1221,7 +1221,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1241,21 +1241,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI UI UX Agency: The AI-Plus-Human Advantage</t>
+          <t>AI Creative Agency for Startups: AI Speed, Human Craft</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ai ui ux agency</t>
+          <t>ai creative agency for startups</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1265,7 +1265,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -1285,42 +1285,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AI Creative Agency for Startups: AI Speed, Human Craft</t>
+          <t>Unlimited Graphic Design Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ai creative agency for startups</t>
+          <t>unlimited graphic design</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
+        <v>38</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1329,38 +1329,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Without the Agency Price Tag</t>
+          <t>Unlimited Graphic Design Service: How AI Cuts Cost, Not Quality</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design</t>
+          <t>unlimited graphic design service</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+        <v>37</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
@@ -1373,31 +1373,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Service: How AI Cuts Cost, Not Quality</t>
+          <t>Subscription Based Website: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design service</t>
+          <t>subscription based website</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>480</v>
+        <v>260</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1417,31 +1417,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Subscription Based Website: What to Expect &amp; Pricing</t>
+          <t>Low Cost Website Design: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>subscription based website</t>
+          <t>low cost website design</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1461,31 +1461,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Low Cost Website Design: A Smarter Way to Brief It</t>
+          <t>Subscription Website: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>low cost website design</t>
+          <t>subscription website</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1505,31 +1505,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Subscription Website: Speed, Scope &amp; Budget</t>
+          <t>Unlimited Design Service Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>subscription website</t>
+          <t>unlimited design service</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1549,31 +1549,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unlimited Design Service: How AI Cuts Cost, Not Quality</t>
+          <t>Graphic Design Monthly Subscription: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>unlimited design service</t>
+          <t>graphic design monthly subscription</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1593,38 +1593,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Graphic Design Monthly Subscription: Speed, Scope &amp; Budget</t>
+          <t>Unlimited Graphic Design Packages: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>graphic design monthly subscription</t>
+          <t>unlimited graphic design packages</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
@@ -1637,31 +1637,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Packages: A Smarter Way to Brief It</t>
+          <t>On Demand Graphic Design: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design packages</t>
+          <t>on demand graphic design</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>On Demand Graphic Design: Faster, Leaner, Smarter</t>
+          <t>Web Design Subscription: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>on demand graphic design</t>
+          <t>web design subscription</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
@@ -1695,24 +1695,24 @@
       <c r="E26" t="n">
         <v>18</v>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -1725,31 +1725,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Web Design Subscription: Quality on a Faster Timeline</t>
+          <t>Subscription Design Services: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>web design subscription</t>
+          <t>subscription design services</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1769,31 +1769,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Subscription Design Services: Faster, Leaner, Smarter</t>
+          <t>Unlimited Design Subscription: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>subscription design services</t>
+          <t>unlimited design subscription</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
         <v>140</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1813,31 +1813,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unlimited Design Subscription Without the Agency Price Tag</t>
+          <t>Low Cost Logo Design Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>unlimited design subscription</t>
+          <t>low cost logo design</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
         <v>140</v>
       </c>
       <c r="E29" t="n">
-        <v>44</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1857,31 +1857,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Low Cost Logo Design: What to Expect &amp; Pricing</t>
+          <t>Affordable Branding Agency: How AI Cuts Cost, Not Quality</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>low cost logo design</t>
+          <t>affordable branding agency</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1901,31 +1901,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Affordable Branding Agency: What to Expect &amp; Pricing</t>
+          <t>Product Design Subscription: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>affordable branding agency</t>
+          <t>product design subscription</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -1945,38 +1945,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Product Design Subscription: Faster, Leaner, Smarter</t>
+          <t>Unlimited Web Development: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>product design subscription</t>
+          <t>unlimited web development</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E32" t="n">
-        <v>15</v>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
@@ -1989,38 +1989,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unlimited Web Development: Quality on a Faster Timeline</t>
+          <t>Subscription Based Design Services: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>unlimited web development</t>
+          <t>subscription based design services</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
@@ -2033,31 +2033,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Subscription Based Design Services: Speed, Scope &amp; Budget</t>
+          <t>Affordable Graphic Design Services: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>subscription based design services</t>
+          <t>affordable graphic design services</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2077,31 +2077,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Affordable Graphic Design Services: Quality on a Faster Timeline</t>
+          <t>Design Subscription Agency: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>affordable graphic design services</t>
+          <t>design subscription agency</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E35" t="n">
-        <v>29</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2121,38 +2121,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Design Subscription Agency: Speed, Scope &amp; Budget</t>
+          <t>Unlimited Graphic Design for Monthly Fee: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>design subscription agency</t>
+          <t>unlimited graphic design for monthly fee</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
@@ -2165,38 +2165,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design for Monthly Fee: A Smarter Way to Brief It</t>
+          <t>Graphic Design Subscription Service: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design for monthly fee</t>
+          <t>graphic design subscription service</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
@@ -2209,38 +2209,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Affordable Brand Voice Development Companies Usa Without the Agency Price Tag</t>
+          <t>Flat Rate Graphic Design Services: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>affordable brand voice development companies usa</t>
+          <t>flat rate graphic design services</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
@@ -2253,31 +2253,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Graphic Design Subscription Service: A Smarter Way to Brief It</t>
+          <t>Best Quick Turnaround Design Services: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>graphic design subscription service</t>
+          <t>best quick turnaround design services</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2297,31 +2297,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flat Rate Graphic Design Services: Quality on a Faster Timeline</t>
+          <t>Design Subscription for SaaS Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>flat rate graphic design services</t>
+          <t>design subscription for saas</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2341,38 +2341,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Affordable Website Marketing Without the Agency Price Tag</t>
+          <t>Affordable Branding Services: How AI Cuts Cost, Not Quality</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>affordable website marketing</t>
+          <t>affordable branding services</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E41" t="n">
-        <v>39</v>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
@@ -2385,31 +2385,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Affordable Website Marketing Services: What to Expect &amp; Pricing</t>
+          <t>Design as a Subscription: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>affordable website marketing services</t>
+          <t>design as a subscription</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2429,31 +2429,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Best Quick Turnaround Design Services Without the Agency Price Tag</t>
+          <t>Product and Web Design Subscription: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>best quick turnaround design services</t>
+          <t>product and web design subscription</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2473,31 +2473,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Design Subscription for SaaS: How AI Cuts Cost, Not Quality</t>
+          <t>Unlimited Graphic Design Subscription Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>design subscription for saas</t>
+          <t>unlimited graphic design subscription</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -2517,38 +2517,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Affordable Branding Services: What to Expect &amp; Pricing</t>
+          <t>Affordable Logo Design Packages: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>affordable branding services</t>
+          <t>affordable logo design packages</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
@@ -2561,38 +2561,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Design as a Subscription: Faster, Leaner, Smarter</t>
+          <t>AI Logos vs a Real Brand Identity: What AI Gets Right (and Where a Studio Wins)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>design as a subscription</t>
+          <t>artificial intelligence logo</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>70</v>
+        <v>1600</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
@@ -2605,38 +2605,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Product and Web Design Subscription: Speed, Scope &amp; Budget</t>
+          <t>AI in Branding: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>product and web design subscription</t>
+          <t>ai in branding</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
@@ -2649,42 +2649,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Subscription: A Smarter Way to Brief It</t>
+          <t>AI vs Human Designers, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design subscription</t>
+          <t>ai vs human designers</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+        <v>10</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2693,38 +2693,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Affordable Logo Design Packages: Faster, Leaner, Smarter</t>
+          <t>Will AI Replace Web Designers? The B2B View</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>affordable logo design packages</t>
+          <t>will ai replace web designers</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>48</v>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+        <v>12</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
@@ -2737,23 +2737,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AI in Branding: What It Means for Your Brand</t>
+          <t>AI Design Trends to Watch in 2026</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ai in branding</t>
+          <t>ai design trends 2026</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2781,23 +2781,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AI vs Human Designers, Explained for B2B Teams</t>
+          <t>The Honest Take on AI and Graphic Design</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ai vs human designers</t>
+          <t>ai and graphic design</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -2805,7 +2805,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Will AI Replace Web Designers? The B2B View</t>
+          <t>The Future of Web Design Is AI + Human</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>will ai replace web designers</t>
+          <t>future of web design with ai</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
@@ -2839,7 +2839,7 @@
       <c r="E52" t="n">
         <v>12</v>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -2849,7 +2849,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -2869,23 +2869,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Honest Take on AI Design Trends 2026</t>
+          <t>AI Impact on Branding for Design Leaders</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>ai design trends 2026</t>
+          <t>ai impact on branding</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -2893,7 +2893,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -2913,23 +2913,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AI and Graphic Design: A Practical 2026 View</t>
+          <t>Human vs AI Design: A Practical 2026 View</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>ai and graphic design</t>
+          <t>human vs ai design</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -2937,7 +2937,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -2957,23 +2957,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rethinking Future of Web Design with AI for Modern Brands</t>
+          <t>Rethinking AI Design Workflow for Modern Brands</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>future of web design with ai</t>
+          <t>ai design workflow</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>18</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -2981,7 +2981,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3001,21 +3001,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AI Impact on Branding for Design Leaders</t>
+          <t>AI for Design Agencies: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ai impact on branding</t>
+          <t>ai for design agencies</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -3025,7 +3025,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Human vs AI Design: What It Means for Your Brand</t>
+          <t>AI Brand Strategy, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>human vs ai design</t>
+          <t>ai brand strategy</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
@@ -3059,7 +3059,7 @@
       <c r="E57" t="n">
         <v>12</v>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -3069,7 +3069,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3089,21 +3089,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AI Design Workflow, Explained for B2B Teams</t>
+          <t>The Honest Take on AI in UX Design</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ai design workflow</t>
+          <t>ai in ux design</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3113,7 +3113,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3133,23 +3133,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Honest Take on AI for Design Agencies</t>
+          <t>Generative AI in Design: A Practical 2026 View</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>ai for design agencies</t>
+          <t>generative ai in design</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>22</v>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -3157,7 +3157,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AI Brand Strategy for Design Leaders</t>
+          <t>Rethinking AI Augmented Design for Modern Brands</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ai brand strategy</t>
+          <t>ai augmented design</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
@@ -3191,7 +3191,7 @@
       <c r="E60" t="n">
         <v>12</v>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -3201,7 +3201,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3221,21 +3221,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AI in UX Design: A Practical 2026 View</t>
+          <t>Designing with AI for Design Leaders</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ai in ux design</t>
+          <t>designing with ai</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3245,7 +3245,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3265,21 +3265,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rethinking Generative AI in Design for Modern Brands</t>
+          <t>AI Design Process: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>generative ai in design</t>
+          <t>ai design process</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>22</v>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3289,7 +3289,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3309,21 +3309,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AI Augmented Design: What It Means for Your Brand</t>
+          <t>Ethics of AI in Design, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>ai augmented design</t>
+          <t>ethics of ai in design</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -3333,7 +3333,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3353,23 +3353,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Designing with AI, Explained for B2B Teams</t>
+          <t>AI Web Design vs a Human Team: The Honest Trade-offs</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>designing with ai</t>
+          <t>ai web design vs human</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -3377,7 +3377,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -3388,138 +3388,6 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>The Honest Take on AI Design Process</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>ai design process</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>16</v>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Ethics of AI in Design: A Practical 2026 View</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>ethics of ai in design</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>10</v>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G66" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Rethinking AI Web Design vs Human for Modern Brands</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>ai web design vs human</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>12</v>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3534,7 +3402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3595,17 +3463,17 @@
       <c r="C2" t="n">
         <v>33</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3638,7 +3506,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3661,17 +3529,17 @@
       <c r="C4" t="n">
         <v>38</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3694,7 +3562,7 @@
       <c r="C5" t="n">
         <v>46</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3704,7 +3572,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3718,92 +3586,92 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>copy website code with ai</t>
+          <t>unlimited graphic design service</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>37</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design service</t>
+          <t>unlimited web design subscription pricing</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>57</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>unlimited web design subscription pricing</t>
+          <t>ai logo suite</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3817,18 +3685,18 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ai logo suite</t>
+          <t>ai architecture design</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>54</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -3836,7 +3704,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3850,14 +3718,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ai architecture design</t>
+          <t>ads creative ai</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -3869,7 +3737,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3883,26 +3751,26 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ads creative ai</t>
+          <t>graphic design subscription</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>390</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3916,26 +3784,26 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>graphic design subscription</t>
+          <t>landing page ai</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3949,14 +3817,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>landing page ai</t>
+          <t>artificial intelligence in web development</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -3968,7 +3836,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -3982,224 +3850,224 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>artificial intelligence in web development</t>
+          <t>subscription based website</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>20</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>copy website with ai</t>
+          <t>low cost website design</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>260</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>subscription based website</t>
+          <t>best ai design app</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>low cost website design</t>
+          <t>galileo ai ui design</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>best ai design app</t>
+          <t>subscription website</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>210</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>galileo ai ui design</t>
+          <t>unlimited graphic design packages</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>210</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>50</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>subscription website</t>
+          <t>unlimited design service</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
         <v>210</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4213,26 +4081,26 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design packages</t>
+          <t>graphic design monthly subscription</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>210</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4246,84 +4114,84 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>unlimited design service</t>
+          <t>branding artificial intelligence</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>52</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>graphic design monthly subscription</t>
+          <t>business card design ai</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>59</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>branding artificial intelligence</t>
+          <t>galileo ai ui design from text</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>28</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4331,7 +4199,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4345,18 +4213,18 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>business card design ai</t>
+          <t>ai content agency</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C25" t="n">
-        <v>59</v>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>46</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -4364,7 +4232,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4378,18 +4246,18 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>galileo ai ui design from text</t>
+          <t>motion graphics ai</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>44</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -4397,7 +4265,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4411,59 +4279,59 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ai content agency</t>
+          <t>on demand graphic design</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C27" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>motion graphics ai</t>
+          <t>unlimited web design</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>170</v>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+        <v>57</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4477,26 +4345,26 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>on demand graphic design</t>
+          <t>ai in branding</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4510,125 +4378,125 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>unlimited web design</t>
+          <t>low cost logo design</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>49</v>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ai in branding</t>
+          <t>ai arch design</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
         <v>140</v>
       </c>
       <c r="C31" t="n">
-        <v>49</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>low cost logo design</t>
+          <t>ai building design</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
         <v>140</v>
       </c>
       <c r="C32" t="n">
-        <v>49</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ai arch design</t>
+          <t>subscription page</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
         <v>140</v>
       </c>
       <c r="C33" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4642,214 +4510,214 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ai building design</t>
+          <t>unlimited design subscription</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
         <v>140</v>
       </c>
       <c r="C34" t="n">
-        <v>42</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>clone a website with ai</t>
+          <t>subscription design services</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
         <v>140</v>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>39</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>subscription page</t>
+          <t>affordable branding agency</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>unlimited design subscription</t>
+          <t>affordable web marketing</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C37" t="n">
-        <v>44</v>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>56</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>subscription design services</t>
+          <t>ai logo white</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>affordable branding agency</t>
+          <t>ai agent agency</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>50</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ai logo white</t>
+          <t>ai websites design</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4859,7 +4727,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4873,51 +4741,51 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ai agent agency</t>
+          <t>affordable graphic design services</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>29</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ai websites design</t>
+          <t>ai motion designer</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -4925,7 +4793,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4939,26 +4807,26 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>clone any website with ai</t>
+          <t>paid subscription services</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -4972,92 +4840,92 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>affordable graphic design services</t>
+          <t>subscription based companies</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>37</v>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ai motion designer</t>
+          <t>product design subscription</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C45" t="n">
-        <v>26</v>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>paid subscription services</t>
+          <t>subscription site</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C46" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5071,59 +4939,59 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>subscription based companies</t>
+          <t>subscription based design services</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C47" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>product design subscription</t>
+          <t>design subscription agency</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5137,59 +5005,59 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>subscription site</t>
+          <t>unlimited graphic design for monthly fee</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>36</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>subscription based design services</t>
+          <t>unlimited web development</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5203,92 +5071,92 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>design subscription agency</t>
+          <t>artificial intelligence for architectural design</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C51" t="n">
-        <v>35</v>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design for monthly fee</t>
+          <t>ai portfolio website</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C52" t="n">
-        <v>36</v>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>unlimited web development</t>
+          <t>flat rate graphic design services</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C53" t="n">
-        <v>17</v>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5302,26 +5170,26 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>affordable brand voice development companies usa</t>
+          <t>graphic design subscription service</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
         <v>90</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5335,26 +5203,26 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>affordable website marketing</t>
+          <t>affordable branding services</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>39</v>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5368,26 +5236,26 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>affordable website marketing services</t>
+          <t>affordable logo design packages</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C56" t="n">
-        <v>41</v>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5401,16 +5269,16 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>artificial intelligence for architectural design</t>
+          <t>best ai for floor plan design</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5420,7 +5288,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5434,18 +5302,18 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>copy any website with ai</t>
+          <t>best ai for architectural design</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C58" t="n">
-        <v>29</v>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>47</v>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -5453,7 +5321,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5467,18 +5335,18 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ai portfolio website</t>
+          <t>ai for website redesign</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C59" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -5486,7 +5354,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5500,59 +5368,59 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>flat rate graphic design services</t>
+          <t>ai web development strategies</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C60" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>graphic design subscription service</t>
+          <t>best quick turnaround design services</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C61" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5566,59 +5434,59 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>affordable branding services</t>
+          <t>subscription website design</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>affordable logo design packages</t>
+          <t>design subscription for saas</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C63" t="n">
-        <v>48</v>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5632,125 +5500,125 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>best ai for floor plan design</t>
+          <t>product and web design subscription</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>42</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G64" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>best ai for architectural design</t>
+          <t>design as a subscription</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C65" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ai for website redesign</t>
+          <t>unlimited graphic design subscription</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G66" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>42</v>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ai web development strategies</t>
+          <t>affordable website and digital marketing packages</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5764,59 +5632,59 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>best quick turnaround design services</t>
+          <t>ai overview logo</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>58</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>subscription website design</t>
+          <t>ai brand intelligence</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5830,158 +5698,158 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>design subscription for saas</t>
+          <t>affordable branding agencies for startups</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>product and web design subscription</t>
+          <t>affordable brand strategy firms</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C71" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>design as a subscription</t>
+          <t>sketch logo ai</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>50</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design subscription</t>
+          <t>best ai website creators</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C73" t="n">
-        <v>42</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Demand now</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>Demand now</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>affordable website and digital marketing packages</t>
+          <t>subscription based website design</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
         <v>50</v>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -5995,26 +5863,26 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>ai overview logo</t>
+          <t>affordable design subscription services</t>
         </is>
       </c>
       <c r="B75" s="4" t="n">
         <v>50</v>
       </c>
       <c r="C75" t="n">
-        <v>58</v>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -6028,26 +5896,26 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>ai brand intelligence</t>
+          <t>graphic subscription</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
         <v>50</v>
       </c>
       <c r="C76" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Demand now</t>
         </is>
@@ -6061,28 +5929,28 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>affordable branding agencies for startups</t>
+          <t>ai brand checks</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+        <v>36</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
@@ -6094,28 +5962,28 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>affordable brand strategy firms</t>
+          <t>ai tv logo</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C78" t="n">
-        <v>16</v>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6127,18 +5995,18 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>sketch logo ai</t>
+          <t>rebrand ai</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>26</v>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -6148,7 +6016,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
@@ -6160,18 +6028,18 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>best ai website creators</t>
+          <t>ai for brand building</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C80" t="n">
-        <v>31</v>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>54</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -6181,7 +6049,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6193,28 +6061,28 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>subscription based website design</t>
+          <t>brand kit ai</t>
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+        <v>28</v>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G81" s="15" t="inlineStr">
@@ -6226,28 +6094,28 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>affordable design subscription services</t>
+          <t>affordable branding services small businesses</t>
         </is>
       </c>
       <c r="B82" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C82" t="n">
-        <v>26</v>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>Fast &amp; Affordable Design</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6259,28 +6127,28 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>graphic subscription</t>
+          <t>artificial intelligence in web applications</t>
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C83" t="n">
-        <v>22</v>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+        <v>57</v>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
@@ -6292,18 +6160,18 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>design to code ai</t>
+          <t>galileo ui ai</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C84" t="n">
-        <v>50</v>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>42</v>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -6313,7 +6181,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Demand now</t>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6325,16 +6193,16 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>ai brand checks</t>
+          <t>ai website design ideas</t>
         </is>
       </c>
       <c r="B85" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C85" t="n">
-        <v>36</v>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6344,7 +6212,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6358,26 +6226,26 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>ai tv logo</t>
+          <t>cheap graphic design services</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
+        <v>56</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6391,26 +6259,26 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>rebrand ai</t>
+          <t>on demand design team</t>
         </is>
       </c>
       <c r="B87" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C87" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6424,26 +6292,26 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>ai for brand building</t>
+          <t>web design subscription model</t>
         </is>
       </c>
       <c r="B88" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C88" t="n">
-        <v>54</v>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6457,26 +6325,26 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>brand kit ai</t>
+          <t>subscription based graphic design</t>
         </is>
       </c>
       <c r="B89" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C89" t="n">
-        <v>28</v>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6490,26 +6358,26 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>affordable branding services small businesses</t>
+          <t>design subscription plan</t>
         </is>
       </c>
       <c r="B90" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C90" t="n">
-        <v>22</v>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6523,18 +6391,18 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>artificial intelligence in web applications</t>
+          <t>ai agent ux</t>
         </is>
       </c>
       <c r="B91" s="4" t="n">
         <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>57</v>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>21</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -6542,7 +6410,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6556,18 +6424,18 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>galileo ui ai</t>
+          <t>ai design subscription</t>
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C92" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -6575,40 +6443,40 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G92" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>ai website design ideas</t>
+          <t>affordable branding</t>
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C93" t="n">
-        <v>44</v>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6622,26 +6490,26 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>cheap graphic design services</t>
+          <t>product marketing ai</t>
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C94" t="n">
-        <v>56</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6655,26 +6523,26 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>on demand design team</t>
+          <t>ai brand development</t>
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6688,26 +6556,26 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>web design subscription model</t>
+          <t>how to use ai for design</t>
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C96" t="n">
-        <v>19</v>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6721,26 +6589,26 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>subscription based graphic design</t>
+          <t>best ai for flyer design</t>
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C97" t="n">
-        <v>26</v>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6754,26 +6622,26 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>design subscription plan</t>
+          <t>best ai model for web design</t>
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C98" t="n">
-        <v>31</v>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6787,26 +6655,26 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>ai agent ux</t>
+          <t>flat rate web design</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C99" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6820,59 +6688,59 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ai design subscription</t>
+          <t>on demand design services</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
         <v>30</v>
       </c>
       <c r="C100" t="n">
-        <v>18</v>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G100" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+        <v>37</v>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>affordable branding</t>
+          <t>cheap one page website</t>
         </is>
       </c>
       <c r="B101" s="4" t="n">
         <v>30</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6886,26 +6754,26 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>product marketing ai</t>
+          <t>ux design subscription</t>
         </is>
       </c>
       <c r="B102" s="4" t="n">
         <v>30</v>
       </c>
       <c r="C102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6919,26 +6787,26 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>ai brand development</t>
+          <t>design com subscription</t>
         </is>
       </c>
       <c r="B103" s="4" t="n">
         <v>30</v>
       </c>
       <c r="C103" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>Fast &amp; Affordable Design</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -6952,18 +6820,18 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>how to use ai for design</t>
+          <t>ai branding agency</t>
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>50</v>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>5</v>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -6971,32 +6839,32 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G104" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>best ai for flyer design</t>
+          <t>ai web design agency</t>
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>47</v>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>5</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -7004,32 +6872,32 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G105" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>best ai model for web design</t>
+          <t>ai design agency</t>
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>51</v>
-      </c>
-      <c r="D106" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>5</v>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -7037,32 +6905,32 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G106" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>clone any website using ai</t>
+          <t>ai ux design agency</t>
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -7070,195 +6938,195 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G107" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>flat rate web design</t>
+          <t>ai webflow agency</t>
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G108" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>on demand design services</t>
+          <t>generative ai design agency</t>
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>37</v>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G109" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>8</v>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>cheap one page website</t>
+          <t>ai brand strategy agency</t>
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>30</v>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G110" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+        <v>6</v>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>ux design subscription</t>
+          <t>ai product design agency</t>
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G111" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>design com subscription</t>
+          <t>ai branding studio</t>
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G112" s="15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>AI-Forward Positioning</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>ai branding agency</t>
+          <t>ai web design studio</t>
         </is>
       </c>
       <c r="B113" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7268,7 +7136,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7282,16 +7150,16 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>ai web design agency</t>
+          <t>ai powered branding agency</t>
         </is>
       </c>
       <c r="B114" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7301,7 +7169,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F114" s="9" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7315,7 +7183,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>ai design agency</t>
+          <t>ai first design agency</t>
         </is>
       </c>
       <c r="B115" s="4" t="n">
@@ -7324,7 +7192,7 @@
       <c r="C115" t="n">
         <v>5</v>
       </c>
-      <c r="D115" s="10" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7334,7 +7202,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7348,7 +7216,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>ai ux design agency</t>
+          <t>ai ui ux agency</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
@@ -7357,7 +7225,7 @@
       <c r="C116" t="n">
         <v>8</v>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7367,7 +7235,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7381,16 +7249,16 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>ai webflow agency</t>
+          <t>ai creative agency for startups</t>
         </is>
       </c>
       <c r="B117" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7400,7 +7268,7 @@
           <t>AI-Forward Positioning</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7414,26 +7282,26 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>generative ai design agency</t>
+          <t>ai vs human designers</t>
         </is>
       </c>
       <c r="B118" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7447,26 +7315,26 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>ai brand strategy agency</t>
+          <t>will ai replace web designers</t>
         </is>
       </c>
       <c r="B119" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7480,26 +7348,26 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>ai product design agency</t>
+          <t>ai design trends 2026</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7513,26 +7381,26 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>ai branding studio</t>
+          <t>ai and graphic design</t>
         </is>
       </c>
       <c r="B121" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7546,26 +7414,26 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>ai web design studio</t>
+          <t>future of web design with ai</t>
         </is>
       </c>
       <c r="B122" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7579,26 +7447,26 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>ai powered branding agency</t>
+          <t>ai impact on branding</t>
         </is>
       </c>
       <c r="B123" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7612,26 +7480,26 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>ai first design agency</t>
+          <t>human vs ai design</t>
         </is>
       </c>
       <c r="B124" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7645,26 +7513,26 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>ai ui ux agency</t>
+          <t>ai design workflow</t>
         </is>
       </c>
       <c r="B125" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7678,26 +7546,26 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>ai creative agency for startups</t>
+          <t>ai for design agencies</t>
         </is>
       </c>
       <c r="B126" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>AI-Forward Positioning</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7711,16 +7579,16 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>ai vs human designers</t>
+          <t>ai brand strategy</t>
         </is>
       </c>
       <c r="B127" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7730,7 +7598,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7744,18 +7612,18 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>will ai replace web designers</t>
+          <t>ai in ux design</t>
         </is>
       </c>
       <c r="B128" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>12</v>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>20</v>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
@@ -7763,7 +7631,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7777,16 +7645,16 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>ai design trends 2026</t>
+          <t>generative ai in design</t>
         </is>
       </c>
       <c r="B129" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>15</v>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7796,7 +7664,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7810,18 +7678,18 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>ai and graphic design</t>
+          <t>ai augmented design</t>
         </is>
       </c>
       <c r="B130" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
@@ -7829,7 +7697,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F130" s="9" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7843,18 +7711,18 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>future of web design with ai</t>
+          <t>designing with ai</t>
         </is>
       </c>
       <c r="B131" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>12</v>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>18</v>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
@@ -7862,7 +7730,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7876,18 +7744,18 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>ai impact on branding</t>
+          <t>ai design process</t>
         </is>
       </c>
       <c r="B132" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>16</v>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
@@ -7895,7 +7763,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7909,16 +7777,16 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>human vs ai design</t>
+          <t>ethics of ai in design</t>
         </is>
       </c>
       <c r="B133" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>12</v>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7928,7 +7796,7 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F133" s="9" t="inlineStr">
+      <c r="F133" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
@@ -7942,18 +7810,18 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>ai design workflow</t>
+          <t>ai web design vs human</t>
         </is>
       </c>
       <c r="B134" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
@@ -7961,309 +7829,12 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="F134" s="9" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>Early-mover bet</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>ai for design agencies</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="n">
-        <v>14</v>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E135" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G135" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>ai brand strategy</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" t="n">
-        <v>12</v>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E136" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G136" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>ai in ux design</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="n">
-        <v>20</v>
-      </c>
-      <c r="D137" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E137" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G137" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>generative ai in design</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" t="n">
-        <v>22</v>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E138" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G138" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>ai augmented design</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" t="n">
-        <v>12</v>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G139" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>designing with ai</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" t="n">
-        <v>18</v>
-      </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E140" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G140" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>ai design process</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" t="n">
-        <v>16</v>
-      </c>
-      <c r="D141" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E141" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G141" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>ethics of ai in design</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" t="n">
-        <v>10</v>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E142" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G142" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>ai web design vs human</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="n">
-        <v>12</v>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E143" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="G143" s="14" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8338,9 +7909,9 @@
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A · AI-Forward Positioning   (16 articles) — 'AI branding agency', 'AI web design agency', 'AI design subscription'. Mostly ~0 volume TODAY = early-mover bets to own the cluster when demand arrives in 1-2 months.
-  B · Fast &amp; Affordable Design (32 articles) — 'unlimited graphic design', 'web design subscription', 'low cost website design'. REAL demand now, and it maps exactly to your new faster / cost-efficient packages (SuperDesign). This is where traffic and leads come from in months 1-3.
-  C · AI + Human Thought Leadership (18 articles) — 'AI vs human designers', 'will AI replace web designers', 'AI in branding'. Evergreen positioning content that earns AI citations (AEO) and reassures buyers. Low volume, high authority value.</t>
+          <t xml:space="preserve">  A · AI-Forward Positioning   (15 articles) — 'AI branding agency', 'AI web design agency', 'AI design subscription'. Mostly ~0 volume TODAY = early-mover bets to own the cluster when demand arrives in 1-2 months.
+  B · Fast &amp; Affordable Design (29 articles) — 'unlimited graphic design', 'web design subscription', 'low cost website design'. REAL demand now, and it maps exactly to your new faster / cost-efficient packages (SuperDesign). This is where traffic and leads come from in months 1-3.
+  C · AI + Human Thought Leadership (19 articles) — 'AI vs human designers', 'will AI replace web designers', 'AI in branding'. Evergreen positioning content that earns AI citations (AEO) and reassures buyers. Low volume, high authority value.</t>
         </is>
       </c>
     </row>
@@ -8354,7 +7925,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>Every article is tagged. 'Demand now' (34) = people search this today, expect ramp in months 2-4. 'Early-mover bet' (32) = ~0 volume today, published to own the term before competitors and before the demand curve. Average difficulty across the plan is just 20.3 — almost all easy wins.</t>
+          <t>Every article is tagged. 'Demand now' (31) = people search this today, expect ramp in months 2-4. 'Early-mover bet' (32) = ~0 volume today, published to own the term before competitors and before the demand curve. Average difficulty across the plan is just 20.0 — almost all easy wins.</t>
         </is>
       </c>
     </row>

--- a/decks/eloqwnt/keyword-research-ai.xlsx
+++ b/decks/eloqwnt/keyword-research-ai.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1373,23 +1373,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Subscription Based Website: What to Expect &amp; Pricing</t>
+          <t>Low Cost Website Design: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>subscription based website</t>
+          <t>low cost website design</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>40</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Low Cost Website Design: A Smarter Way to Brief It</t>
+          <t>Unlimited Design Service: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>low cost website design</t>
+          <t>unlimited design service</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
@@ -1461,23 +1461,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Subscription Website: Speed, Scope &amp; Budget</t>
+          <t>Graphic Design Monthly Subscription Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>subscription website</t>
+          <t>graphic design monthly subscription</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>49</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1505,23 +1505,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unlimited Design Service Without the Agency Price Tag</t>
+          <t>Unlimited Graphic Design Packages: How AI Cuts Cost, Not Quality</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>unlimited design service</t>
+          <t>unlimited graphic design packages</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>50</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
@@ -1549,23 +1549,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Graphic Design Monthly Subscription: What to Expect &amp; Pricing</t>
+          <t>On Demand Graphic Design: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>graphic design monthly subscription</t>
+          <t>on demand graphic design</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>18</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Packages: Speed, Scope &amp; Budget</t>
+          <t>Web Design Subscription: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design packages</t>
+          <t>web design subscription</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>18</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
@@ -1637,23 +1637,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>On Demand Graphic Design: Faster, Leaner, Smarter</t>
+          <t>Subscription Design Services: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>on demand graphic design</t>
+          <t>subscription design services</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>39</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
@@ -1681,23 +1681,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Web Design Subscription: Quality on a Faster Timeline</t>
+          <t>Unlimited Design Subscription: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>web design subscription</t>
+          <t>unlimited design subscription</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>44</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -1725,19 +1725,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Subscription Design Services: A Smarter Way to Brief It</t>
+          <t>Low Cost Logo Design: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>subscription design services</t>
+          <t>low cost logo design</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
         <v>140</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
@@ -1769,23 +1769,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Unlimited Design Subscription: Quality on a Faster Timeline</t>
+          <t>Affordable Branding Agency: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>unlimited design subscription</t>
+          <t>affordable branding agency</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>10</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -1813,23 +1813,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Low Cost Logo Design Without the Agency Price Tag</t>
+          <t>Product Design Subscription: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>low cost logo design</t>
+          <t>product design subscription</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="E29" t="n">
-        <v>49</v>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>15</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Affordable Branding Agency: How AI Cuts Cost, Not Quality</t>
+          <t>Unlimited Web Development: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>affordable branding agency</t>
+          <t>unlimited web development</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>17</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
@@ -1901,19 +1901,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Product Design Subscription: A Smarter Way to Brief It</t>
+          <t>Subscription Based Design Services Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>product design subscription</t>
+          <t>subscription based design services</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -1945,19 +1945,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unlimited Web Development: Faster, Leaner, Smarter</t>
+          <t>Affordable Graphic Design Services: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>unlimited web development</t>
+          <t>affordable graphic design services</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
@@ -1989,23 +1989,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Subscription Based Design Services: What to Expect &amp; Pricing</t>
+          <t>Design Subscription Agency: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>subscription based design services</t>
+          <t>design subscription agency</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>35</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Affordable Graphic Design Services: Faster, Leaner, Smarter</t>
+          <t>Unlimited Graphic Design for Monthly Fee Without the Agency Price Tag</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>affordable graphic design services</t>
+          <t>unlimited graphic design for monthly fee</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E34" t="n">
-        <v>29</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>36</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
@@ -2077,23 +2077,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Design Subscription Agency: What to Expect &amp; Pricing</t>
+          <t>Graphic Design Subscription Service: How AI Cuts Cost, Not Quality</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>design subscription agency</t>
+          <t>graphic design subscription service</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E35" t="n">
-        <v>35</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>16</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -2121,19 +2121,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design for Monthly Fee: Speed, Scope &amp; Budget</t>
+          <t>Flat Rate Graphic Design Services: Speed, Scope &amp; Budget</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design for monthly fee</t>
+          <t>flat rate graphic design services</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E36" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
@@ -2165,23 +2165,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Graphic Design Subscription Service: Speed, Scope &amp; Budget</t>
+          <t>Best Quick Turnaround Design Services: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>graphic design subscription service</t>
+          <t>best quick turnaround design services</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>3</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -2209,23 +2209,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Flat Rate Graphic Design Services: Faster, Leaner, Smarter</t>
+          <t>Design Subscription for SaaS: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>flat rate graphic design services</t>
+          <t>design subscription for saas</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E38" t="n">
-        <v>32</v>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>4</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -2253,19 +2253,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Best Quick Turnaround Design Services: Quality on a Faster Timeline</t>
+          <t>Affordable Branding Services: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>best quick turnaround design services</t>
+          <t>affordable branding services</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Design Subscription for SaaS Without the Agency Price Tag</t>
+          <t>Design as a Subscription: What to Expect &amp; Pricing</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>design subscription for saas</t>
+          <t>design as a subscription</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>17</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -2341,23 +2341,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Affordable Branding Services: How AI Cuts Cost, Not Quality</t>
+          <t>Product and Web Design Subscription: A Smarter Way to Brief It</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>affordable branding services</t>
+          <t>product and web design subscription</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>32</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -2385,23 +2385,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Design as a Subscription: A Smarter Way to Brief It</t>
+          <t>Unlimited Graphic Design Subscription: Faster, Leaner, Smarter</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>design as a subscription</t>
+          <t>unlimited graphic design subscription</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>42</v>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Product and Web Design Subscription: Quality on a Faster Timeline</t>
+          <t>Affordable Logo Design Packages: Quality on a Faster Timeline</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>product and web design subscription</t>
+          <t>affordable logo design packages</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
@@ -2473,28 +2473,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Unlimited Graphic Design Subscription Without the Agency Price Tag</t>
+          <t>AI Logos vs a Real Brand Identity: What AI Gets Right (and Where a Studio Wins)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>unlimited graphic design subscription</t>
+          <t>artificial intelligence logo</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>70</v>
+        <v>1600</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
@@ -2517,28 +2517,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Affordable Logo Design Packages: What to Expect &amp; Pricing</t>
+          <t>AI in Branding: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>affordable logo design packages</t>
+          <t>ai in branding</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E45" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Fast &amp; Affordable Design</t>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>AI + Human Thought Leadership</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
@@ -2561,23 +2561,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AI Logos vs a Real Brand Identity: What AI Gets Right (and Where a Studio Wins)</t>
+          <t>AI vs Human Designers, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>artificial intelligence logo</t>
+          <t>ai vs human designers</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>33</v>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>10</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -2585,9 +2585,9 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>Demand now</t>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2605,23 +2605,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AI in Branding: What It Means for Your Brand</t>
+          <t>Will AI Replace Web Designers? The B2B View</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>ai in branding</t>
+          <t>will ai replace web designers</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>49</v>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>12</v>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
@@ -2629,9 +2629,9 @@
           <t>AI + Human Thought Leadership</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>Demand now</t>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Early-mover bet</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2649,23 +2649,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AI vs Human Designers, Explained for B2B Teams</t>
+          <t>AI Design Trends to Watch in 2026</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ai vs human designers</t>
+          <t>ai design trends 2026</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>15</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -2693,23 +2693,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Will AI Replace Web Designers? The B2B View</t>
+          <t>The Honest Take on AI and Graphic Design</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>will ai replace web designers</t>
+          <t>ai and graphic design</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -2737,23 +2737,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AI Design Trends to Watch in 2026</t>
+          <t>The Future of Web Design Is AI + Human</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ai design trends 2026</t>
+          <t>future of web design with ai</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>15</v>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>12</v>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -2781,23 +2781,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Honest Take on AI and Graphic Design</t>
+          <t>AI Impact on Branding for Design Leaders</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ai and graphic design</t>
+          <t>ai impact on branding</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>20</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>10</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Future of Web Design Is AI + Human</t>
+          <t>Human vs AI Design: A Practical 2026 View</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>future of web design with ai</t>
+          <t>human vs ai design</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
@@ -2869,23 +2869,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AI Impact on Branding for Design Leaders</t>
+          <t>Rethinking AI Design Workflow for Modern Brands</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>ai impact on branding</t>
+          <t>ai design workflow</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>18</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -2913,19 +2913,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Human vs AI Design: A Practical 2026 View</t>
+          <t>AI for Design Agencies: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>human vs ai design</t>
+          <t>ai for design agencies</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -2957,23 +2957,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rethinking AI Design Workflow for Modern Brands</t>
+          <t>AI Brand Strategy, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>ai design workflow</t>
+          <t>ai brand strategy</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>12</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -3001,23 +3001,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AI for Design Agencies: What It Means for Your Brand</t>
+          <t>The Honest Take on AI in UX Design</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ai for design agencies</t>
+          <t>ai in ux design</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -3045,23 +3045,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AI Brand Strategy, Explained for B2B Teams</t>
+          <t>Generative AI in Design: A Practical 2026 View</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ai brand strategy</t>
+          <t>generative ai in design</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>22</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -3089,23 +3089,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Honest Take on AI in UX Design</t>
+          <t>Rethinking AI Augmented Design for Modern Brands</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ai in ux design</t>
+          <t>ai augmented design</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>12</v>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Generative AI in Design: A Practical 2026 View</t>
+          <t>Designing with AI for Design Leaders</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>generative ai in design</t>
+          <t>designing with ai</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rethinking AI Augmented Design for Modern Brands</t>
+          <t>AI Design Process: What It Means for Your Brand</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ai augmented design</t>
+          <t>ai design process</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>16</v>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -3221,23 +3221,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Designing with AI for Design Leaders</t>
+          <t>Ethics of AI in Design, Explained for B2B Teams</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>designing with ai</t>
+          <t>ethics of ai in design</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>18</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>10</v>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -3265,23 +3265,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AI Design Process: What It Means for Your Brand</t>
+          <t>AI Web Design vs a Human Team: The Honest Trade-offs</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ai design process</t>
+          <t>ai web design vs human</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>16</v>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>12</v>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
@@ -3300,94 +3300,6 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Ethics of AI in Design, Explained for B2B Teams</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>ethics of ai in design</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>10</v>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>AI Web Design vs a Human Team: The Honest Trade-offs</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>ai web design vs human</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>12</v>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>AI + Human Thought Leadership</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Early-mover bet</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3874,9 +3786,9 @@
           <t>Demand now</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -4006,9 +3918,9 @@
           <t>Demand now</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7822,7 @@
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  A · AI-Forward Positioning   (15 articles) — 'AI branding agency', 'AI web design agency', 'AI design subscription'. Mostly ~0 volume TODAY = early-mover bets to own the cluster when demand arrives in 1-2 months.
-  B · Fast &amp; Affordable Design (29 articles) — 'unlimited graphic design', 'web design subscription', 'low cost website design'. REAL demand now, and it maps exactly to your new faster / cost-efficient packages (SuperDesign). This is where traffic and leads come from in months 1-3.
+  B · Fast &amp; Affordable Design (27 articles) — 'unlimited graphic design', 'web design subscription', 'low cost website design'. REAL demand now, and it maps exactly to your new faster / cost-efficient packages (SuperDesign). This is where traffic and leads come from in months 1-3.
   C · AI + Human Thought Leadership (19 articles) — 'AI vs human designers', 'will AI replace web designers', 'AI in branding'. Evergreen positioning content that earns AI citations (AEO) and reassures buyers. Low volume, high authority value.</t>
         </is>
       </c>
@@ -7925,7 +7837,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>Every article is tagged. 'Demand now' (31) = people search this today, expect ramp in months 2-4. 'Early-mover bet' (32) = ~0 volume today, published to own the term before competitors and before the demand curve. Average difficulty across the plan is just 20.0 — almost all easy wins.</t>
+          <t>Every article is tagged. 'Demand now' (29) = people search this today, expect ramp in months 2-4. 'Early-mover bet' (32) = ~0 volume today, published to own the term before competitors and before the demand curve. Average difficulty across the plan is just 20.0 — almost all easy wins.</t>
         </is>
       </c>
     </row>
